--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6616-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6616-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F2A278C-ACEB-40D1-87F5-F83B9517C904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{666561DA-6AE5-4CA4-8582-631A7FA77488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{74800431-C6A3-449A-9F7E-CB1B2FE3C70E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D983B995-2D00-4E72-943D-26B94D90ED7C}"/>
   </bookViews>
   <sheets>
     <sheet name="6616-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1460,25 +1460,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47BEEC3C-F0C6-4D77-AE89-EBF751C292C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38056DCA-6858-4B15-8ADD-F0FB530D9CD8}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1512,7 +1512,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1668,7 +1668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2021</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2020</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>29</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2019</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2018</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2017</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2016</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35" t="s">
         <v>41</v>
       </c>
